--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.86082658319682</v>
+        <v>2.739884319769484</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0688397054073</v>
+        <v>2.773686452128687</v>
       </c>
       <c r="E2" t="n">
-        <v>11.74004882946598</v>
+        <v>1.907757934788222</v>
       </c>
       <c r="F2" t="n">
-        <v>11.75100746562059</v>
+        <v>1.909538713163346</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.45365744422055</v>
+        <v>2.998719334685839</v>
       </c>
       <c r="D3" t="n">
-        <v>18.46154441595344</v>
+        <v>3.000000967592435</v>
       </c>
       <c r="E3" t="n">
-        <v>11.74004882946598</v>
+        <v>1.907757934788222</v>
       </c>
       <c r="F3" t="n">
-        <v>11.75100746562059</v>
+        <v>1.909538713163346</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.29060860106211</v>
+        <v>7.359723897672593</v>
       </c>
       <c r="D4" t="n">
-        <v>45.04644220752129</v>
+        <v>7.320046858722209</v>
       </c>
       <c r="E4" t="n">
-        <v>11.74004882946598</v>
+        <v>1.907757934788222</v>
       </c>
       <c r="F4" t="n">
-        <v>11.75100746562059</v>
+        <v>1.909538713163346</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.62889696449878</v>
+        <v>6.114695756731051</v>
       </c>
       <c r="D5" t="n">
-        <v>38.38208202641923</v>
+        <v>6.237088329293126</v>
       </c>
       <c r="E5" t="n">
-        <v>11.74004882946598</v>
+        <v>1.907757934788222</v>
       </c>
       <c r="F5" t="n">
-        <v>11.75100746562059</v>
+        <v>1.909538713163346</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.28024783850681</v>
+        <v>6.545540273757357</v>
       </c>
       <c r="D6" t="n">
-        <v>40.56194175399179</v>
+        <v>6.591315535023666</v>
       </c>
       <c r="E6" t="n">
-        <v>11.74004882946598</v>
+        <v>1.907757934788222</v>
       </c>
       <c r="F6" t="n">
-        <v>11.75100746562059</v>
+        <v>1.909538713163346</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
